--- a/outputs/sesc_api_relatorio_qualidade.xlsx
+++ b/outputs/sesc_api_relatorio_qualidade.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-09-15 16:55:50</t>
+          <t>2026-09-29 16:09:00</t>
         </is>
       </c>
     </row>
@@ -11116,27 +11116,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>01.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Programas Sociais</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.281.961.168,00</t>
+          <t>128.870.696,00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.281.961.168,00</t>
+          <t>128.870.696,00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.757.914.812,96</t>
+          <t>54.116.592,17</t>
         </is>
       </c>
     </row>
@@ -11148,27 +11148,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01.01</t>
+          <t>01.01.01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Educação Infantil</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>128.870.696,00</t>
+          <t>6.514.480,00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>128.870.696,00</t>
+          <t>6.514.480,00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.116.592,17</t>
+          <t>2.292.102,63</t>
         </is>
       </c>
     </row>
@@ -11180,27 +11180,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01.01.01</t>
+          <t>01.01.01.01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Educação Infantil</t>
+          <t>Creche</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.514.480,00</t>
+          <t>145.089,00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.514.480,00</t>
+          <t>145.089,00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.292.102,63</t>
+          <t>2.024.322,48</t>
         </is>
       </c>
     </row>
@@ -11212,27 +11212,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01.01.01.01</t>
+          <t>01.01.01.02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Creche</t>
+          <t>Pré-escola</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>145.089,00</t>
+          <t>6.369.391,00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>145.089,00</t>
+          <t>6.369.391,00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.024.322,48</t>
+          <t>267.780,15</t>
         </is>
       </c>
     </row>
@@ -11244,27 +11244,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01.01.01.02</t>
+          <t>01.01.04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pré-escola</t>
+          <t>Educação de Jovens e Adultos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.369.391,00</t>
+          <t>32.000,00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.369.391,00</t>
+          <t>32.000,00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>267.780,15</t>
+          <t>42.322,07</t>
         </is>
       </c>
     </row>
@@ -11276,12 +11276,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01.01.04</t>
+          <t>01.01.04.03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Educação de Jovens e Adultos</t>
+          <t>Séries/Etapas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11308,27 +11308,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01.01.04.03</t>
+          <t>01.01.05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Séries/Etapas</t>
+          <t>Educação Ampliada</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.000,00</t>
+          <t>60.734.698,00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.000,00</t>
+          <t>60.734.698,00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.322,07</t>
+          <t>25.754.635,67</t>
         </is>
       </c>
     </row>
@@ -11340,27 +11340,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01.01.05</t>
+          <t>01.01.05.01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Educação Ampliada</t>
+          <t>Ações formativas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>60.734.698,00</t>
+          <t>26.369.170,00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60.734.698,00</t>
+          <t>26.369.170,00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.754.635,67</t>
+          <t>10.072.076,89</t>
         </is>
       </c>
     </row>
@@ -11372,27 +11372,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01.01.05.01</t>
+          <t>01.01.05.02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ações formativas</t>
+          <t>Ações mediadas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26.369.170,00</t>
+          <t>26.486.992,00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.369.170,00</t>
+          <t>26.486.992,00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.072.076,89</t>
+          <t>12.136.166,78</t>
         </is>
       </c>
     </row>
@@ -11404,27 +11404,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01.01.05.02</t>
+          <t>01.01.05.03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ações mediadas</t>
+          <t>Apresentações</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26.486.992,00</t>
+          <t>3.851.557,00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.486.992,00</t>
+          <t>3.851.557,00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.136.166,78</t>
+          <t>937.033,47</t>
         </is>
       </c>
     </row>
@@ -11436,27 +11436,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01.01.05.03</t>
+          <t>01.01.05.04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Apresentações</t>
+          <t>Eventos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.851.557,00</t>
+          <t>1.919.045,00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.851.557,00</t>
+          <t>1.919.045,00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>937.033,47</t>
+          <t>1.142.306,16</t>
         </is>
       </c>
     </row>
@@ -11468,27 +11468,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01.01.05.04</t>
+          <t>01.01.05.05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eventos</t>
+          <t>Exposição</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.919.045,00</t>
+          <t>2.107.934,00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.919.045,00</t>
+          <t>2.107.934,00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.142.306,16</t>
+          <t>1.467.052,37</t>
         </is>
       </c>
     </row>
@@ -11500,27 +11500,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01.01.05.05</t>
+          <t>01.01.06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Exposição</t>
+          <t>Apoio à Prog. Finalística - Educação</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.107.934,00</t>
+          <t>61.589.518,00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.107.934,00</t>
+          <t>61.589.518,00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.467.052,37</t>
+          <t>26.027.531,80</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01.01.06</t>
+          <t>01.01.06.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Apoio à Prog. Finalística - Educação</t>
+          <t>Apoio à prog. finalística - Educação</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11564,27 +11564,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01.01.06.01</t>
+          <t>01.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Apoio à prog. finalística - Educação</t>
+          <t>Saúde</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>61.589.518,00</t>
+          <t>655.199.652,00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>61.589.518,00</t>
+          <t>655.199.652,00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.027.531,80</t>
+          <t>282.199.252,70</t>
         </is>
       </c>
     </row>
@@ -11596,27 +11596,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01.02</t>
+          <t>01.02.07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Alimentação e Nutrição</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>655.199.652,00</t>
+          <t>437.445.993,00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>655.199.652,00</t>
+          <t>437.445.993,00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>282.199.252,70</t>
+          <t>181.432.323,53</t>
         </is>
       </c>
     </row>
@@ -11628,27 +11628,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01.02.07</t>
+          <t>01.02.07.04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alimentação e Nutrição</t>
+          <t>Lanche</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>437.445.993,00</t>
+          <t>255.683.554,00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>437.445.993,00</t>
+          <t>255.683.554,00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>181.432.323,53</t>
+          <t>104.027.335,57</t>
         </is>
       </c>
     </row>
@@ -11660,27 +11660,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01.02.07.04</t>
+          <t>01.02.07.05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lanche</t>
+          <t>Produtos gastronômicos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>255.683.554,00</t>
+          <t>470.823,00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>255.683.554,00</t>
+          <t>470.823,00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>104.027.335,57</t>
+          <t>29.087,35</t>
         </is>
       </c>
     </row>
@@ -11692,27 +11692,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01.02.07.05</t>
+          <t>01.02.07.06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Produtos gastronômicos</t>
+          <t>Refeição</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>470.823,00</t>
+          <t>180.299.168,00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>470.823,00</t>
+          <t>180.299.168,00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29.087,35</t>
+          <t>76.627.549,85</t>
         </is>
       </c>
     </row>
@@ -11724,27 +11724,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01.02.07.06</t>
+          <t>01.02.07.07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Refeição</t>
+          <t>Ações formativas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>180.299.168,00</t>
+          <t>652.111,00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>180.299.168,00</t>
+          <t>652.111,00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>76.627.549,85</t>
+          <t>472.118,62</t>
         </is>
       </c>
     </row>
